--- a/FileRaw/Regole scadenzario.xlsx
+++ b/FileRaw/Regole scadenzario.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://confidentdental-my.sharepoint.com/personal/amministrazione_confident_dental/Documents/Desktop/CONFIDENT/00-CCH/00-Contabilità/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreadepaoli/Documents/Coding/cDen/chipdent/FileRaw/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="90" documentId="8_{4E49AE69-12D0-428F-8BE7-307CE17A9938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7F6F8F9-DE42-4F91-B006-9532F1FC29CB}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F0D640F6-6466-4DCC-877C-CCED56EAD078}"/>
+    <workbookView xWindow="-100" yWindow="660" windowWidth="25780" windowHeight="17000" xr2:uid="{F0D640F6-6466-4DCC-877C-CCED56EAD078}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -412,18 +412,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -432,15 +420,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -463,6 +442,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -472,9 +454,27 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -933,7 +933,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema di Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1250,295 +1250,298 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2523AA5D-F510-4801-A48A-910EDC31DB7C}">
   <dimension ref="D1:E55"/>
-  <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="3" width="8.88671875" style="2"/>
-    <col min="4" max="4" width="58.88671875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="47.33203125" style="18" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="2"/>
+    <col min="1" max="3" width="8.83203125" style="2"/>
+    <col min="4" max="4" width="58.83203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="47.33203125" style="11" customWidth="1"/>
+    <col min="6" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="4:5" ht="4.2" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-    </row>
-    <row r="2" spans="4:5" ht="42.6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="3" spans="4:5" ht="4.2" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-    </row>
-    <row r="4" spans="4:5" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D4" s="23" t="s">
+    <row r="1" spans="4:5" ht="4.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+    </row>
+    <row r="2" spans="4:5" ht="42.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="3" spans="4:5" ht="4.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+    </row>
+    <row r="4" spans="4:5" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D4" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="E4" s="23"/>
-    </row>
-    <row r="5" spans="4:5" ht="4.2" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-    </row>
-    <row r="6" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="E4" s="17"/>
+    </row>
+    <row r="5" spans="4:5" ht="4.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+    </row>
+    <row r="6" spans="4:5" ht="13" x14ac:dyDescent="0.15">
       <c r="D6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="4:5" ht="13" x14ac:dyDescent="0.15">
       <c r="D7" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D8" s="4" t="s">
+    <row r="8" spans="4:5" ht="13" x14ac:dyDescent="0.15">
+      <c r="D8" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="13" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D9" s="5"/>
-      <c r="E9" s="21" t="s">
+    <row r="9" spans="4:5" ht="13" x14ac:dyDescent="0.15">
+      <c r="D9" s="21"/>
+      <c r="E9" s="14" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D10" s="6"/>
-      <c r="E10" s="22" t="s">
+    <row r="10" spans="4:5" ht="13" x14ac:dyDescent="0.15">
+      <c r="D10" s="22"/>
+      <c r="E10" s="15" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="4:5" ht="13" x14ac:dyDescent="0.15">
       <c r="D11" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="E11" s="9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="4:5" ht="22.8" x14ac:dyDescent="0.2">
-      <c r="D12" s="4" t="s">
+    <row r="12" spans="4:5" ht="26" x14ac:dyDescent="0.15">
+      <c r="D12" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="20" t="s">
+      <c r="E12" s="13" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D13" s="7"/>
-      <c r="E13" s="22" t="s">
+    <row r="13" spans="4:5" ht="13" x14ac:dyDescent="0.15">
+      <c r="D13" s="23"/>
+      <c r="E13" s="15" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="4:5" ht="13" x14ac:dyDescent="0.15">
       <c r="D14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="E14" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D15" s="4" t="s">
+    <row r="15" spans="4:5" ht="13" x14ac:dyDescent="0.15">
+      <c r="D15" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="E15" s="20" t="s">
+      <c r="E15" s="13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D16" s="6"/>
-      <c r="E16" s="22" t="s">
+    <row r="16" spans="4:5" ht="13" x14ac:dyDescent="0.15">
+      <c r="D16" s="22"/>
+      <c r="E16" s="15" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="4:5" ht="12.6" x14ac:dyDescent="0.2">
-      <c r="D21" s="24" t="s">
+    <row r="21" spans="4:5" ht="13" x14ac:dyDescent="0.15">
+      <c r="D21" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="E21" s="25"/>
-    </row>
-    <row r="22" spans="4:5" ht="22.8" x14ac:dyDescent="0.2">
-      <c r="D22" s="8" t="s">
+      <c r="E21" s="19"/>
+    </row>
+    <row r="22" spans="4:5" ht="26" x14ac:dyDescent="0.15">
+      <c r="D22" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="E22" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="4:5" ht="2.4" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D23" s="15"/>
-      <c r="E23" s="17"/>
-    </row>
-    <row r="24" spans="4:5" ht="22.8" x14ac:dyDescent="0.2">
-      <c r="D24" s="9" t="s">
+    <row r="23" spans="4:5" ht="2.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D23" s="8"/>
+      <c r="E23" s="10"/>
+    </row>
+    <row r="24" spans="4:5" ht="26" x14ac:dyDescent="0.15">
+      <c r="D24" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E24" s="18" t="s">
+      <c r="E24" s="11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="25" spans="4:5" ht="2.4" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D25" s="15"/>
-      <c r="E25" s="17"/>
-    </row>
-    <row r="26" spans="4:5" ht="22.8" x14ac:dyDescent="0.2">
-      <c r="D26" s="9" t="s">
+    <row r="25" spans="4:5" ht="2.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D25" s="8"/>
+      <c r="E25" s="10"/>
+    </row>
+    <row r="26" spans="4:5" ht="13" x14ac:dyDescent="0.15">
+      <c r="D26" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E26" s="19" t="s">
+      <c r="E26" s="12" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="27" spans="4:5" ht="2.4" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D27" s="15"/>
-      <c r="E27" s="17"/>
-    </row>
-    <row r="28" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D28" s="9" t="s">
+    <row r="27" spans="4:5" ht="2.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D27" s="8"/>
+      <c r="E27" s="10"/>
+    </row>
+    <row r="28" spans="4:5" ht="13" x14ac:dyDescent="0.15">
+      <c r="D28" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E28" s="18" t="s">
+      <c r="E28" s="11" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="29" spans="4:5" ht="2.4" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D29" s="15"/>
-      <c r="E29" s="17"/>
-    </row>
-    <row r="30" spans="4:5" ht="22.8" x14ac:dyDescent="0.2">
-      <c r="D30" s="9" t="s">
+    <row r="29" spans="4:5" ht="2.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D29" s="8"/>
+      <c r="E29" s="10"/>
+    </row>
+    <row r="30" spans="4:5" ht="13" x14ac:dyDescent="0.15">
+      <c r="D30" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E30" s="18" t="s">
+      <c r="E30" s="11" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="31" spans="4:5" ht="2.4" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D31" s="15"/>
-      <c r="E31" s="17"/>
-    </row>
-    <row r="32" spans="4:5" ht="22.8" x14ac:dyDescent="0.2">
-      <c r="D32" s="9" t="s">
+    <row r="31" spans="4:5" ht="2.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D31" s="8"/>
+      <c r="E31" s="10"/>
+    </row>
+    <row r="32" spans="4:5" ht="26" x14ac:dyDescent="0.15">
+      <c r="D32" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="4:5" ht="2.4" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D33" s="15"/>
-      <c r="E33" s="17"/>
-    </row>
-    <row r="37" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D37" s="10" t="s">
+    <row r="33" spans="4:5" ht="2.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D33" s="8"/>
+      <c r="E33" s="10"/>
+    </row>
+    <row r="37" spans="4:5" ht="13" x14ac:dyDescent="0.15">
+      <c r="D37" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E37" s="9" t="s">
+      <c r="E37" s="5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="38" spans="4:5" ht="45.6" x14ac:dyDescent="0.2">
-      <c r="D38" s="11" t="s">
+    <row r="38" spans="4:5" ht="39" x14ac:dyDescent="0.15">
+      <c r="D38" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E38" s="9" t="s">
+      <c r="E38" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="39" spans="4:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="4:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D39" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E39" s="9" t="s">
+      <c r="E39" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="40" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D40" s="12" t="s">
+    <row r="40" spans="4:5" ht="13" x14ac:dyDescent="0.15">
+      <c r="D40" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="E40" s="20" t="s">
+      <c r="E40" s="13" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="41" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D41" s="12"/>
-      <c r="E41" s="21" t="s">
+    <row r="41" spans="4:5" ht="13" x14ac:dyDescent="0.15">
+      <c r="D41" s="24"/>
+      <c r="E41" s="14" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="4:5" ht="22.8" x14ac:dyDescent="0.2">
-      <c r="D42" s="13"/>
-      <c r="E42" s="22" t="s">
+    <row r="42" spans="4:5" ht="26" x14ac:dyDescent="0.15">
+      <c r="D42" s="25"/>
+      <c r="E42" s="15" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="43" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D43" s="12" t="s">
+    <row r="43" spans="4:5" ht="13" x14ac:dyDescent="0.15">
+      <c r="D43" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="E43" s="20" t="s">
+      <c r="E43" s="13" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D44" s="12"/>
-      <c r="E44" s="21" t="s">
+    <row r="44" spans="4:5" ht="13" x14ac:dyDescent="0.15">
+      <c r="D44" s="24"/>
+      <c r="E44" s="14" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D45" s="13"/>
-      <c r="E45" s="22" t="s">
+    <row r="45" spans="4:5" ht="13" x14ac:dyDescent="0.15">
+      <c r="D45" s="25"/>
+      <c r="E45" s="15" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="52" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="52" spans="4:5" ht="13" x14ac:dyDescent="0.15">
       <c r="D52" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E52" s="9" t="s">
+      <c r="E52" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="53" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D53" s="4" t="s">
+    <row r="53" spans="4:5" ht="13" x14ac:dyDescent="0.15">
+      <c r="D53" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="E53" s="20" t="s">
+      <c r="E53" s="13" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="54" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D54" s="5"/>
-      <c r="E54" s="21" t="s">
+    <row r="54" spans="4:5" ht="13" x14ac:dyDescent="0.15">
+      <c r="D54" s="21"/>
+      <c r="E54" s="14" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="55" spans="4:5" ht="23.4" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D55" s="6"/>
-      <c r="E55" s="22" t="s">
+    <row r="55" spans="4:5" ht="23.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D55" s="22"/>
+      <c r="E55" s="15" t="s">
         <v>36</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D21:E21"/>
     <mergeCell ref="D53:D55"/>
     <mergeCell ref="D8:D10"/>
     <mergeCell ref="D12:D13"/>
     <mergeCell ref="D15:D16"/>
     <mergeCell ref="D40:D42"/>
     <mergeCell ref="D43:D45"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D21:E21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 This document is classified as EOLO - C2 General</oddFooter>
+  </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/FileRaw/Regole scadenzario.xlsx
+++ b/FileRaw/Regole scadenzario.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreadepaoli/Documents/Coding/cDen/chipdent/FileRaw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="90" documentId="8_{4E49AE69-12D0-428F-8BE7-307CE17A9938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7F6F8F9-DE42-4F91-B006-9532F1FC29CB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19B449EB-B097-974E-B804-A9826DCD9D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-100" yWindow="660" windowWidth="25780" windowHeight="17000" xr2:uid="{F0D640F6-6466-4DCC-877C-CCED56EAD078}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="25780" windowHeight="17000" xr2:uid="{F0D640F6-6466-4DCC-877C-CCED56EAD078}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="48">
   <si>
     <t xml:space="preserve">BONIFICI IN GENERALE </t>
   </si>
@@ -149,9 +149,6 @@
     <t>inserire come data scadenza 30/31 del mese corrente rispetto la data fattura - inserire alert</t>
   </si>
   <si>
-    <t>alcuni fornitori possono essere associati a "tipo" diversi (esempio: medici/direzione sanitaria) - inserire alert</t>
-  </si>
-  <si>
     <t xml:space="preserve">per tutti gli altri fornitori </t>
   </si>
   <si>
@@ -185,7 +182,7 @@
     <t>se manca il mese nell'oggetto- inserire alert</t>
   </si>
   <si>
-    <t>match tra nome fornitore e tipo</t>
+    <t>leggi categoria e sottocategoria dal fornitore</t>
   </si>
 </sst>
 </file>
@@ -442,6 +439,24 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -453,24 +468,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1259,30 +1256,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="4:5" ht="4.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
     </row>
     <row r="2" spans="4:5" ht="42.5" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="3" spans="4:5" ht="4.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
     </row>
     <row r="4" spans="4:5" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D4" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="E4" s="17"/>
+      <c r="D4" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" s="23"/>
     </row>
     <row r="5" spans="4:5" ht="4.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
     </row>
     <row r="6" spans="4:5" ht="13" x14ac:dyDescent="0.15">
       <c r="D6" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="4:5" ht="13" x14ac:dyDescent="0.15">
@@ -1294,7 +1291,7 @@
       </c>
     </row>
     <row r="8" spans="4:5" ht="13" x14ac:dyDescent="0.15">
-      <c r="D8" s="20" t="s">
+      <c r="D8" s="16" t="s">
         <v>3</v>
       </c>
       <c r="E8" s="13" t="s">
@@ -1302,13 +1299,13 @@
       </c>
     </row>
     <row r="9" spans="4:5" ht="13" x14ac:dyDescent="0.15">
-      <c r="D9" s="21"/>
+      <c r="D9" s="17"/>
       <c r="E9" s="14" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="10" spans="4:5" ht="13" x14ac:dyDescent="0.15">
-      <c r="D10" s="22"/>
+      <c r="D10" s="18"/>
       <c r="E10" s="15" t="s">
         <v>32</v>
       </c>
@@ -1322,7 +1319,7 @@
       </c>
     </row>
     <row r="12" spans="4:5" ht="26" x14ac:dyDescent="0.15">
-      <c r="D12" s="20" t="s">
+      <c r="D12" s="16" t="s">
         <v>8</v>
       </c>
       <c r="E12" s="13" t="s">
@@ -1330,9 +1327,9 @@
       </c>
     </row>
     <row r="13" spans="4:5" ht="13" x14ac:dyDescent="0.15">
-      <c r="D13" s="23"/>
+      <c r="D13" s="19"/>
       <c r="E13" s="15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="4:5" ht="13" x14ac:dyDescent="0.15">
@@ -1344,7 +1341,7 @@
       </c>
     </row>
     <row r="15" spans="4:5" ht="13" x14ac:dyDescent="0.15">
-      <c r="D15" s="20" t="s">
+      <c r="D15" s="16" t="s">
         <v>12</v>
       </c>
       <c r="E15" s="13" t="s">
@@ -1352,16 +1349,16 @@
       </c>
     </row>
     <row r="16" spans="4:5" ht="13" x14ac:dyDescent="0.15">
-      <c r="D16" s="22"/>
+      <c r="D16" s="18"/>
       <c r="E16" s="15" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="21" spans="4:5" ht="13" x14ac:dyDescent="0.15">
-      <c r="D21" s="18" t="s">
+      <c r="D21" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="E21" s="19"/>
+      <c r="E21" s="25"/>
     </row>
     <row r="22" spans="4:5" ht="26" x14ac:dyDescent="0.15">
       <c r="D22" s="4" t="s">
@@ -1377,10 +1374,10 @@
     </row>
     <row r="24" spans="4:5" ht="26" x14ac:dyDescent="0.15">
       <c r="D24" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E24" s="11" t="s">
         <v>37</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="25" spans="4:5" ht="2.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -1389,10 +1386,10 @@
     </row>
     <row r="26" spans="4:5" ht="13" x14ac:dyDescent="0.15">
       <c r="D26" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="4:5" ht="2.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -1401,10 +1398,10 @@
     </row>
     <row r="28" spans="4:5" ht="13" x14ac:dyDescent="0.15">
       <c r="D28" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29" spans="4:5" ht="2.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -1413,10 +1410,10 @@
     </row>
     <row r="30" spans="4:5" ht="13" x14ac:dyDescent="0.15">
       <c r="D30" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31" spans="4:5" ht="2.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -1457,7 +1454,7 @@
       </c>
     </row>
     <row r="40" spans="4:5" ht="13" x14ac:dyDescent="0.15">
-      <c r="D40" s="24" t="s">
+      <c r="D40" s="20" t="s">
         <v>23</v>
       </c>
       <c r="E40" s="13" t="s">
@@ -1465,19 +1462,19 @@
       </c>
     </row>
     <row r="41" spans="4:5" ht="13" x14ac:dyDescent="0.15">
-      <c r="D41" s="24"/>
+      <c r="D41" s="20"/>
       <c r="E41" s="14" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="42" spans="4:5" ht="26" x14ac:dyDescent="0.15">
-      <c r="D42" s="25"/>
+      <c r="D42" s="21"/>
       <c r="E42" s="15" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="43" spans="4:5" ht="13" x14ac:dyDescent="0.15">
-      <c r="D43" s="24" t="s">
+      <c r="D43" s="20" t="s">
         <v>26</v>
       </c>
       <c r="E43" s="13" t="s">
@@ -1485,13 +1482,13 @@
       </c>
     </row>
     <row r="44" spans="4:5" ht="13" x14ac:dyDescent="0.15">
-      <c r="D44" s="24"/>
+      <c r="D44" s="20"/>
       <c r="E44" s="14" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="45" spans="4:5" ht="13" x14ac:dyDescent="0.15">
-      <c r="D45" s="25"/>
+      <c r="D45" s="21"/>
       <c r="E45" s="15" t="s">
         <v>27</v>
       </c>
@@ -1505,38 +1502,34 @@
       </c>
     </row>
     <row r="53" spans="4:5" ht="13" x14ac:dyDescent="0.15">
-      <c r="D53" s="20" t="s">
+      <c r="D53" s="16" t="s">
         <v>31</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="54" spans="4:5" ht="13" x14ac:dyDescent="0.15">
-      <c r="D54" s="21"/>
-      <c r="E54" s="14" t="s">
-        <v>48</v>
-      </c>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="54" spans="4:5" x14ac:dyDescent="0.15">
+      <c r="D54" s="17"/>
+      <c r="E54" s="14"/>
     </row>
     <row r="55" spans="4:5" ht="23.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D55" s="22"/>
-      <c r="E55" s="15" t="s">
-        <v>36</v>
-      </c>
+      <c r="D55" s="18"/>
+      <c r="E55" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D21:E21"/>
     <mergeCell ref="D53:D55"/>
     <mergeCell ref="D8:D10"/>
     <mergeCell ref="D12:D13"/>
     <mergeCell ref="D15:D16"/>
     <mergeCell ref="D40:D42"/>
     <mergeCell ref="D43:D45"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D21:E21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
